--- a/tests/testthat/excel/mapping_neu_weighted.xlsx
+++ b/tests/testthat/excel/mapping_neu_weighted.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\Projects\UW git\crosstabser\tests\testthat\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D6001F-F433-4A6D-B91C-02D20974FF2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F9B2EF-4064-4F05-830F-E4DC2DECE23E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15045" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15045" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
     <definedName name="V_Projektname">Config!$B$21</definedName>
     <definedName name="V_Projektverzeichnis">Config!$B$20</definedName>
     <definedName name="V_Scenario">Config!$B$16</definedName>
-    <definedName name="V_ScenDetail">Macro!$E$3:$BB$44</definedName>
+    <definedName name="V_ScenDetail">Macro!$E$3:$BB$42</definedName>
     <definedName name="V_ScenName">Config!$C$16</definedName>
     <definedName name="V_TemplatePath">Config!$B$27</definedName>
     <definedName name="V_Variablen">#REF!</definedName>
@@ -50,8 +50,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -210,7 +208,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="328">
   <si>
     <t>Make script</t>
   </si>
@@ -677,19 +675,7 @@
     <t>-1,-2,-999/-199</t>
   </si>
   <si>
-    <t>Miss2</t>
-  </si>
-  <si>
-    <t>Invalid value 2</t>
-  </si>
-  <si>
     <t>x</t>
-  </si>
-  <si>
-    <t>Miss3</t>
-  </si>
-  <si>
-    <t>Invalid value 3</t>
   </si>
   <si>
     <t>Overall filter</t>
@@ -927,9 +913,6 @@
   </si>
   <si>
     <t>mw</t>
-  </si>
-  <si>
-    <t>Miss1</t>
   </si>
   <si>
     <t>RowVar</t>
@@ -1204,6 +1187,12 @@
   <si>
     <t>ts: dplyr::matches("q2_\\d+$") &amp; -c(q2_00, q2_99) &amp; where(\(x) length(unique(x)) &gt; 1)</t>
   </si>
+  <si>
+    <t>-1,-3,-2</t>
+  </si>
+  <si>
+    <t>Invalid</t>
+  </si>
 </sst>
 </file>
 
@@ -1405,7 +1394,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1455,6 +1444,7 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="1" quotePrefix="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1760,13 +1750,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>390600</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>132945</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>117000</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1997,11 +1987,8 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Hinweis"/>
       <sheetName val="R"/>
@@ -2491,7 +2478,7 @@
         <v>2</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="E15" s="10"/>
     </row>
@@ -2555,10 +2542,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="33" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="B23" s="33" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2641,7 +2628,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="33" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="B35" s="34">
         <v>-2</v>
@@ -2728,7 +2715,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AMJ44"/>
+  <dimension ref="A1:AMJ42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.42578125" style="15" customWidth="1"/>
@@ -3216,7 +3203,7 @@
     </row>
     <row r="5" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B5" s="20" t="s">
         <v>149</v>
@@ -3228,7 +3215,7 @@
         <v>151</v>
       </c>
       <c r="E5" s="29" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="F5" s="29" t="str">
         <f>E5</f>
@@ -3286,7 +3273,7 @@
     </row>
     <row r="6" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A6" s="27" t="s">
-        <v>239</v>
+        <v>327</v>
       </c>
       <c r="B6" s="20" t="s">
         <v>152</v>
@@ -3297,161 +3284,161 @@
       <c r="D6" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="E6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="F6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="G6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="H6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="I6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="J6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="K6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="L6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="M6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="N6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="O6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="P6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="Q6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="R6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="S6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="T6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="U6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="V6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="W6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="X6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="Y6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="Z6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="AA6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="AB6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="AC6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="AD6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="AE6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="AF6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="AG6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="AH6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="AI6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="AJ6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="AK6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="AL6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="AM6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="AN6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="AO6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="AP6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="AQ6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="AR6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="AS6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="AT6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="AU6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="AV6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="AW6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="AX6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="AY6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="AZ6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="BA6" s="14">
-        <v>-1</v>
-      </c>
-      <c r="BB6" s="14">
-        <v>-1</v>
+      <c r="E6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="F6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="G6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="H6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="I6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="J6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="K6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="L6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="M6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="N6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="O6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="P6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="Q6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="R6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="S6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="T6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="U6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="V6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="W6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="X6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="Y6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="Z6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="AA6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="AB6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="AC6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="AD6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="AE6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="AF6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="AG6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="AH6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="AI6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="AJ6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="AK6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="AL6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="AM6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="AN6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="AO6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="AP6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="AQ6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="AR6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="AS6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="AT6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="AU6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="AV6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="AW6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="AX6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="AY6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="AZ6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="BA6" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="BB6" s="37" t="s">
+        <v>326</v>
       </c>
       <c r="BD6" s="19"/>
     </row>
     <row r="7" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A7" s="27" t="s">
-        <v>155</v>
+        <v>221</v>
       </c>
       <c r="B7" s="20" t="s">
         <v>156</v>
@@ -3459,334 +3446,128 @@
       <c r="C7" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="D7" s="20"/>
-      <c r="E7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="F7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="G7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="H7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="I7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="J7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="K7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="L7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="M7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="N7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="O7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="P7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="Q7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="R7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="S7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="T7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="U7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="V7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="W7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="X7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="Y7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="Z7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="AA7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="AB7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="AC7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="AD7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="AE7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="AF7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="AG7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="AH7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="AI7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="AJ7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="AK7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="AL7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="AM7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="AN7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="AO7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="AP7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="AQ7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="AR7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="AS7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="AT7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="AU7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="AV7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="AW7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="AX7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="AY7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="AZ7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="BA7" s="14">
-        <v>-3</v>
-      </c>
-      <c r="BB7" s="14">
-        <v>-3</v>
-      </c>
+      <c r="D7" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="14"/>
+      <c r="P7" s="14"/>
+      <c r="Q7" s="14"/>
+      <c r="R7" s="14"/>
+      <c r="S7" s="14"/>
+      <c r="T7" s="14"/>
+      <c r="U7" s="14"/>
+      <c r="V7" s="14"/>
+      <c r="W7" s="14"/>
+      <c r="X7" s="14"/>
+      <c r="Y7" s="14"/>
+      <c r="Z7" s="14"/>
+      <c r="AA7" s="14"/>
+      <c r="AB7" s="14"/>
+      <c r="AC7" s="14"/>
+      <c r="AD7" s="14"/>
+      <c r="AE7" s="14"/>
+      <c r="AF7" s="14"/>
+      <c r="AG7" s="14"/>
+      <c r="AH7" s="14"/>
+      <c r="AI7" s="14"/>
+      <c r="AJ7" s="14"/>
+      <c r="AK7" s="14"/>
+      <c r="AL7" s="14"/>
+      <c r="AM7" s="14"/>
+      <c r="AN7" s="14"/>
+      <c r="AO7" s="14"/>
+      <c r="AP7" s="14"/>
+      <c r="AQ7" s="14"/>
+      <c r="AR7" s="14"/>
+      <c r="AS7" s="14"/>
+      <c r="AT7" s="14"/>
+      <c r="AU7" s="14"/>
+      <c r="AV7" s="14"/>
+      <c r="AW7" s="14"/>
+      <c r="AX7" s="14"/>
+      <c r="AY7" s="14"/>
+      <c r="AZ7" s="14"/>
+      <c r="BA7" s="14"/>
+      <c r="BB7" s="14"/>
       <c r="BD7" s="19"/>
     </row>
     <row r="8" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A8" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="B8" s="20" t="s">
+      <c r="A8" s="20"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+      <c r="T8" s="14"/>
+      <c r="U8" s="14"/>
+      <c r="V8" s="14"/>
+      <c r="W8" s="14"/>
+      <c r="X8" s="14"/>
+      <c r="Y8" s="14"/>
+      <c r="Z8" s="14"/>
+      <c r="AA8" s="14"/>
+      <c r="AB8" s="14"/>
+      <c r="AC8" s="14"/>
+      <c r="AD8" s="14"/>
+      <c r="AE8" s="14"/>
+      <c r="AF8" s="14"/>
+      <c r="AG8" s="14"/>
+      <c r="AH8" s="14"/>
+      <c r="AI8" s="14"/>
+      <c r="AJ8" s="14"/>
+      <c r="AK8" s="14"/>
+      <c r="AL8" s="14"/>
+      <c r="AM8" s="14"/>
+      <c r="AN8" s="14"/>
+      <c r="AO8" s="14"/>
+      <c r="AP8" s="14"/>
+      <c r="AQ8" s="14"/>
+      <c r="AR8" s="14"/>
+      <c r="AS8" s="14"/>
+      <c r="AT8" s="14"/>
+      <c r="AU8" s="14"/>
+      <c r="AV8" s="14"/>
+      <c r="AW8" s="14"/>
+      <c r="AX8" s="14"/>
+      <c r="AY8" s="14"/>
+      <c r="AZ8" s="14"/>
+      <c r="BA8" s="14"/>
+      <c r="BB8" s="14"/>
+      <c r="BD8" s="19"/>
+    </row>
+    <row r="9" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A9" s="20" t="s">
         <v>159</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="D8" s="20"/>
-      <c r="E8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="F8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="G8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="H8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="I8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="J8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="K8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="L8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="M8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="N8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="O8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="P8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="Q8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="R8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="S8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="T8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="U8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="V8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="W8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="X8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="Y8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="Z8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="AA8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="AB8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="AC8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="AD8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="AE8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="AF8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="AG8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="AH8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="AI8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="AJ8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="AK8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="AL8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="AM8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="AN8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="AO8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="AP8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="AQ8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="AR8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="AS8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="AT8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="AU8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="AV8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="AW8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="AX8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="AY8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="AZ8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="BA8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="BB8" s="14">
-        <v>-2</v>
-      </c>
-      <c r="BD8" s="19"/>
-    </row>
-    <row r="9" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A9" s="27" t="s">
-        <v>225</v>
       </c>
       <c r="B9" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="20"/>
+      <c r="D9" s="20" t="s">
         <v>161</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>162</v>
       </c>
       <c r="E9" s="14"/>
       <c r="F9" s="14"/>
@@ -3841,9 +3622,13 @@
       <c r="BD9" s="19"/>
     </row>
     <row r="10" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A10" s="20"/>
+      <c r="A10" s="20" t="s">
+        <v>162</v>
+      </c>
       <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
+      <c r="C10" s="20" t="s">
+        <v>155</v>
+      </c>
       <c r="D10" s="20"/>
       <c r="E10" s="14"/>
       <c r="F10" s="14"/>
@@ -3898,18 +3683,18 @@
       <c r="BD10" s="19"/>
     </row>
     <row r="11" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="21" t="s">
         <v>163</v>
       </c>
       <c r="B11" s="20" t="s">
         <v>164</v>
       </c>
       <c r="C11" s="20"/>
-      <c r="D11" s="20" t="s">
-        <v>165</v>
-      </c>
+      <c r="D11" s="20"/>
       <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
+      <c r="F11" s="14" t="b">
+        <v>1</v>
+      </c>
       <c r="G11" s="14"/>
       <c r="H11" s="14"/>
       <c r="I11" s="14"/>
@@ -3962,11 +3747,11 @@
     </row>
     <row r="12" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B12" s="20"/>
       <c r="C12" s="20" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D12" s="20"/>
       <c r="E12" s="14"/>
@@ -4022,17 +3807,17 @@
       <c r="BD12" s="19"/>
     </row>
     <row r="13" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="B13" s="20" t="s">
         <v>167</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>168</v>
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="20"/>
       <c r="E13" s="14"/>
-      <c r="F13" s="14" t="b">
-        <v>1</v>
+      <c r="F13" s="14" t="s">
+        <v>244</v>
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="14"/>
@@ -4086,13 +3871,15 @@
     </row>
     <row r="14" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B14" s="20"/>
       <c r="C14" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="D14" s="20"/>
+        <v>155</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>169</v>
+      </c>
       <c r="E14" s="14"/>
       <c r="F14" s="14"/>
       <c r="G14" s="14"/>
@@ -4146,7 +3933,7 @@
       <c r="BD14" s="19"/>
     </row>
     <row r="15" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="21" t="s">
         <v>170</v>
       </c>
       <c r="B15" s="20" t="s">
@@ -4155,9 +3942,7 @@
       <c r="C15" s="20"/>
       <c r="D15" s="20"/>
       <c r="E15" s="14"/>
-      <c r="F15" s="14" t="s">
-        <v>249</v>
-      </c>
+      <c r="F15" s="14"/>
       <c r="G15" s="14"/>
       <c r="H15" s="14"/>
       <c r="I15" s="14"/>
@@ -4209,300 +3994,398 @@
       <c r="BD15" s="19"/>
     </row>
     <row r="16" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="B16" s="20"/>
+      <c r="B16" s="20" t="s">
+        <v>173</v>
+      </c>
       <c r="C16" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>173</v>
-      </c>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="14"/>
-      <c r="P16" s="14"/>
-      <c r="Q16" s="14"/>
-      <c r="R16" s="14"/>
-      <c r="S16" s="14"/>
-      <c r="T16" s="14"/>
-      <c r="U16" s="14"/>
-      <c r="V16" s="14"/>
-      <c r="W16" s="14"/>
-      <c r="X16" s="14"/>
-      <c r="Y16" s="14"/>
-      <c r="Z16" s="14"/>
-      <c r="AA16" s="14"/>
-      <c r="AB16" s="14"/>
-      <c r="AC16" s="14"/>
-      <c r="AD16" s="14"/>
-      <c r="AE16" s="14"/>
-      <c r="AF16" s="14"/>
-      <c r="AG16" s="14"/>
-      <c r="AH16" s="14"/>
-      <c r="AI16" s="14"/>
-      <c r="AJ16" s="14"/>
-      <c r="AK16" s="14"/>
-      <c r="AL16" s="14"/>
-      <c r="AM16" s="14"/>
-      <c r="AN16" s="14"/>
-      <c r="AO16" s="14"/>
-      <c r="AP16" s="14"/>
-      <c r="AQ16" s="14"/>
-      <c r="AR16" s="14"/>
-      <c r="AS16" s="14"/>
-      <c r="AT16" s="14"/>
-      <c r="AU16" s="14"/>
-      <c r="AV16" s="14"/>
-      <c r="AW16" s="14"/>
-      <c r="AX16" s="14"/>
-      <c r="AY16" s="14"/>
-      <c r="AZ16" s="14"/>
-      <c r="BA16" s="14"/>
-      <c r="BB16" s="14"/>
+        <v>174</v>
+      </c>
+      <c r="D16" s="20"/>
+      <c r="E16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="H16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="I16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="J16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="K16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="L16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="M16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="N16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="O16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="P16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="R16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="S16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="T16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="U16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="V16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="W16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="X16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="Y16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="AA16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="AC16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="AD16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="AE16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="AF16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="AG16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="AH16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="AI16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="AJ16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="AK16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="AL16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="AN16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="AO16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="AP16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="AQ16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="AR16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="AS16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="AT16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="AU16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="AV16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="AW16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="AX16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="AY16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="AZ16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="BA16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="BB16" s="14" t="s">
+        <v>175</v>
+      </c>
       <c r="BD16" s="19"/>
     </row>
     <row r="17" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="C17" s="20"/>
+      <c r="A17" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20" t="s">
+        <v>155</v>
+      </c>
       <c r="D17" s="20"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="14"/>
-      <c r="O17" s="14"/>
-      <c r="P17" s="14"/>
-      <c r="Q17" s="14"/>
-      <c r="R17" s="14"/>
-      <c r="S17" s="14"/>
-      <c r="T17" s="14"/>
-      <c r="U17" s="14"/>
-      <c r="V17" s="14"/>
-      <c r="W17" s="14"/>
-      <c r="X17" s="14"/>
-      <c r="Y17" s="14"/>
-      <c r="Z17" s="14"/>
-      <c r="AA17" s="14"/>
-      <c r="AB17" s="14"/>
-      <c r="AC17" s="14"/>
-      <c r="AD17" s="14"/>
-      <c r="AE17" s="14"/>
-      <c r="AF17" s="14"/>
-      <c r="AG17" s="14"/>
-      <c r="AH17" s="14"/>
-      <c r="AI17" s="14"/>
-      <c r="AJ17" s="14"/>
-      <c r="AK17" s="14"/>
-      <c r="AL17" s="14"/>
-      <c r="AM17" s="14"/>
-      <c r="AN17" s="14"/>
-      <c r="AO17" s="14"/>
-      <c r="AP17" s="14"/>
-      <c r="AQ17" s="14"/>
-      <c r="AR17" s="14"/>
-      <c r="AS17" s="14"/>
-      <c r="AT17" s="14"/>
-      <c r="AU17" s="14"/>
-      <c r="AV17" s="14"/>
-      <c r="AW17" s="14"/>
-      <c r="AX17" s="14"/>
-      <c r="AY17" s="14"/>
-      <c r="AZ17" s="14"/>
-      <c r="BA17" s="14"/>
-      <c r="BB17" s="14"/>
+      <c r="E17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="J17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="K17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="L17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="M17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="N17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="O17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="P17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="R17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="S17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="T17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="U17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="V17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="W17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="X17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="Y17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="Z17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="AA17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="AC17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="AD17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="AE17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="AF17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="AG17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="AH17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="AI17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="AJ17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="AK17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="AL17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="AM17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="AN17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="AO17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="AP17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="AQ17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="AR17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="AS17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="AT17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="AV17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="AW17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="AX17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="AY17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="AZ17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="BA17" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="BB17" s="14" t="s">
+        <v>177</v>
+      </c>
       <c r="BD17" s="19"/>
     </row>
     <row r="18" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A18" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>177</v>
-      </c>
+      <c r="A18" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="B18" s="20"/>
       <c r="C18" s="20" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="D18" s="20"/>
-      <c r="E18" s="14" t="s">
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="14"/>
+      <c r="P18" s="14"/>
+      <c r="Q18" s="14"/>
+      <c r="R18" s="14"/>
+      <c r="S18" s="14"/>
+      <c r="T18" s="14"/>
+      <c r="U18" s="14"/>
+      <c r="V18" s="14"/>
+      <c r="W18" s="14"/>
+      <c r="X18" s="14"/>
+      <c r="Y18" s="14"/>
+      <c r="Z18" s="14"/>
+      <c r="AA18" s="14"/>
+      <c r="AB18" s="14"/>
+      <c r="AC18" s="14"/>
+      <c r="AD18" s="14"/>
+      <c r="AE18" s="14"/>
+      <c r="AF18" s="14"/>
+      <c r="AG18" s="14"/>
+      <c r="AH18" s="14"/>
+      <c r="AI18" s="14"/>
+      <c r="AJ18" s="14"/>
+      <c r="AK18" s="14"/>
+      <c r="AL18" s="14"/>
+      <c r="AM18" s="14"/>
+      <c r="AN18" s="14"/>
+      <c r="AO18" s="14"/>
+      <c r="AP18" s="14"/>
+      <c r="AQ18" s="14"/>
+      <c r="AR18" s="14"/>
+      <c r="AS18" s="14"/>
+      <c r="AT18" s="14"/>
+      <c r="AU18" s="14"/>
+      <c r="AV18" s="14"/>
+      <c r="AW18" s="14"/>
+      <c r="AX18" s="14"/>
+      <c r="AY18" s="14"/>
+      <c r="AZ18" s="14"/>
+      <c r="BA18" s="14"/>
+      <c r="BB18" s="14"/>
+      <c r="BD18" s="19"/>
+    </row>
+    <row r="19" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A19" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="F18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="G18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="H18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="I18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="J18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="K18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="L18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="M18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="N18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="O18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="P18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="R18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="S18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="T18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="U18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="V18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="W18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="X18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="Y18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="Z18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AA18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AB18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AC18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AD18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AE18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AF18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AG18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AH18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AI18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AJ18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AK18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AL18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AM18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AN18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AO18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AP18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AQ18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AR18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AS18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AT18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AU18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AV18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AW18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AX18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AY18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AZ18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="BA18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="BB18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="BD18" s="19"/>
-    </row>
-    <row r="19" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A19" s="20" t="s">
+      <c r="B19" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="20" t="s">
-        <v>157</v>
-      </c>
+      <c r="C19" s="20"/>
       <c r="D19" s="20"/>
       <c r="E19" s="14" t="s">
         <v>181</v>
@@ -4660,11 +4543,13 @@
       <c r="A20" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="B20" s="20"/>
-      <c r="C20" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="D20" s="20"/>
+      <c r="B20" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20" t="s">
+        <v>184</v>
+      </c>
       <c r="E20" s="14"/>
       <c r="F20" s="14"/>
       <c r="G20" s="14"/>
@@ -4718,177 +4603,75 @@
       <c r="BD20" s="19"/>
     </row>
     <row r="21" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A21" s="21" t="s">
-        <v>183</v>
-      </c>
-      <c r="B21" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="C21" s="20"/>
+      <c r="A21" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20" t="s">
+        <v>155</v>
+      </c>
       <c r="D21" s="20"/>
-      <c r="E21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="F21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="G21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="H21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="I21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="J21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="K21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="L21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="M21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="N21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="O21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="P21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="R21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="S21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="T21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="U21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="V21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="W21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="X21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="Y21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="Z21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="AA21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="AB21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="AC21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="AD21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="AE21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="AF21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="AG21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="AH21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="AI21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="AJ21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="AK21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="AL21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="AM21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="AN21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="AO21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="AP21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="AQ21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="AR21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="AS21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="AT21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="AU21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="AV21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="AW21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="AX21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="AY21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="AZ21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="BA21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="BB21" s="14" t="s">
-        <v>185</v>
-      </c>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="14"/>
+      <c r="N21" s="14"/>
+      <c r="O21" s="14"/>
+      <c r="P21" s="14"/>
+      <c r="Q21" s="14"/>
+      <c r="R21" s="14"/>
+      <c r="S21" s="14"/>
+      <c r="T21" s="14"/>
+      <c r="U21" s="14"/>
+      <c r="V21" s="14"/>
+      <c r="W21" s="14"/>
+      <c r="X21" s="14"/>
+      <c r="Y21" s="14"/>
+      <c r="Z21" s="14"/>
+      <c r="AA21" s="14"/>
+      <c r="AB21" s="14"/>
+      <c r="AC21" s="14"/>
+      <c r="AD21" s="14"/>
+      <c r="AE21" s="14"/>
+      <c r="AF21" s="14"/>
+      <c r="AG21" s="14"/>
+      <c r="AH21" s="14"/>
+      <c r="AI21" s="14"/>
+      <c r="AJ21" s="14"/>
+      <c r="AK21" s="14"/>
+      <c r="AL21" s="14"/>
+      <c r="AM21" s="14"/>
+      <c r="AN21" s="14"/>
+      <c r="AO21" s="14"/>
+      <c r="AP21" s="14"/>
+      <c r="AQ21" s="14"/>
+      <c r="AR21" s="14"/>
+      <c r="AS21" s="14"/>
+      <c r="AT21" s="14"/>
+      <c r="AU21" s="14"/>
+      <c r="AV21" s="14"/>
+      <c r="AW21" s="14"/>
+      <c r="AX21" s="14"/>
+      <c r="AY21" s="14"/>
+      <c r="AZ21" s="14"/>
+      <c r="BA21" s="14"/>
+      <c r="BB21" s="14"/>
       <c r="BD21" s="19"/>
     </row>
     <row r="22" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="B22" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20" t="s">
-        <v>188</v>
-      </c>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="D22" s="20"/>
       <c r="E22" s="14"/>
       <c r="F22" s="14"/>
       <c r="G22" s="14"/>
@@ -4943,11 +4726,11 @@
     </row>
     <row r="23" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B23" s="20"/>
       <c r="C23" s="20" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D23" s="20"/>
       <c r="E23" s="14"/>
@@ -5004,11 +4787,11 @@
     </row>
     <row r="24" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A24" s="20" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B24" s="20"/>
       <c r="C24" s="20" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D24" s="20"/>
       <c r="E24" s="14"/>
@@ -5065,459 +4848,561 @@
     </row>
     <row r="25" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A25" s="20" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B25" s="20"/>
       <c r="C25" s="20" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D25" s="20"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14"/>
-      <c r="L25" s="14"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="14"/>
-      <c r="O25" s="14"/>
-      <c r="P25" s="14"/>
-      <c r="Q25" s="14"/>
-      <c r="R25" s="14"/>
-      <c r="S25" s="14"/>
-      <c r="T25" s="14"/>
-      <c r="U25" s="14"/>
-      <c r="V25" s="14"/>
-      <c r="W25" s="14"/>
-      <c r="X25" s="14"/>
-      <c r="Y25" s="14"/>
-      <c r="Z25" s="14"/>
-      <c r="AA25" s="14"/>
-      <c r="AB25" s="14"/>
-      <c r="AC25" s="14"/>
-      <c r="AD25" s="14"/>
-      <c r="AE25" s="14"/>
-      <c r="AF25" s="14"/>
-      <c r="AG25" s="14"/>
-      <c r="AH25" s="14"/>
-      <c r="AI25" s="14"/>
-      <c r="AJ25" s="14"/>
-      <c r="AK25" s="14"/>
-      <c r="AL25" s="14"/>
-      <c r="AM25" s="14"/>
-      <c r="AN25" s="14"/>
-      <c r="AO25" s="14"/>
-      <c r="AP25" s="14"/>
-      <c r="AQ25" s="14"/>
-      <c r="AR25" s="14"/>
-      <c r="AS25" s="14"/>
-      <c r="AT25" s="14"/>
-      <c r="AU25" s="14"/>
-      <c r="AV25" s="14"/>
-      <c r="AW25" s="14"/>
-      <c r="AX25" s="14"/>
-      <c r="AY25" s="14"/>
-      <c r="AZ25" s="14"/>
-      <c r="BA25" s="14"/>
-      <c r="BB25" s="14"/>
+      <c r="E25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="G25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="H25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="J25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="K25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="L25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="M25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="N25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="O25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="P25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="R25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="S25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="T25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="U25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="V25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="W25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="X25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="Y25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="Z25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="AA25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="AB25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="AC25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="AD25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="AE25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="AF25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="AG25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="AH25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="AI25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="AJ25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="AK25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="AL25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="AN25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="AO25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="AP25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="AQ25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="AR25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="AS25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="AT25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="AU25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="AV25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="AW25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="AX25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="AY25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="AZ25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="BA25" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="BB25" s="14" t="s">
+        <v>190</v>
+      </c>
       <c r="BD25" s="19"/>
     </row>
     <row r="26" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="B26" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="B26" s="20"/>
       <c r="C26" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="D26" s="20"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
-      <c r="K26" s="14"/>
-      <c r="L26" s="14"/>
-      <c r="M26" s="14"/>
-      <c r="N26" s="14"/>
-      <c r="O26" s="14"/>
-      <c r="P26" s="14"/>
-      <c r="Q26" s="14"/>
-      <c r="R26" s="14"/>
-      <c r="S26" s="14"/>
-      <c r="T26" s="14"/>
-      <c r="U26" s="14"/>
-      <c r="V26" s="14"/>
-      <c r="W26" s="14"/>
-      <c r="X26" s="14"/>
-      <c r="Y26" s="14"/>
-      <c r="Z26" s="14"/>
-      <c r="AA26" s="14"/>
-      <c r="AB26" s="14"/>
-      <c r="AC26" s="14"/>
-      <c r="AD26" s="14"/>
-      <c r="AE26" s="14"/>
-      <c r="AF26" s="14"/>
-      <c r="AG26" s="14"/>
-      <c r="AH26" s="14"/>
-      <c r="AI26" s="14"/>
-      <c r="AJ26" s="14"/>
-      <c r="AK26" s="14"/>
-      <c r="AL26" s="14"/>
-      <c r="AM26" s="14"/>
-      <c r="AN26" s="14"/>
-      <c r="AO26" s="14"/>
-      <c r="AP26" s="14"/>
-      <c r="AQ26" s="14"/>
-      <c r="AR26" s="14"/>
-      <c r="AS26" s="14"/>
-      <c r="AT26" s="14"/>
-      <c r="AU26" s="14"/>
-      <c r="AV26" s="14"/>
-      <c r="AW26" s="14"/>
-      <c r="AX26" s="14"/>
-      <c r="AY26" s="14"/>
-      <c r="AZ26" s="14"/>
-      <c r="BA26" s="14"/>
-      <c r="BB26" s="14"/>
+        <v>193</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="H26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="I26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="J26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="K26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="L26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="M26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="N26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="O26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="P26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="R26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="S26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="T26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="U26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="V26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="W26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="X26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="Y26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="Z26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="AA26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="AB26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="AC26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="AD26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="AE26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="AF26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="AG26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="AH26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="AI26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="AJ26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="AK26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="AL26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="AM26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="AN26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="AO26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="AP26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="AQ26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="AR26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="AS26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="AT26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="AU26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="AV26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="AW26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="AX26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="AY26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="AZ26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="BA26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="BB26" s="14" t="s">
+        <v>195</v>
+      </c>
       <c r="BD26" s="19"/>
     </row>
     <row r="27" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A27" s="20" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B27" s="20"/>
       <c r="C27" s="20" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D27" s="20"/>
       <c r="E27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="K27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="L27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="M27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="N27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="O27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="P27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="R27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="S27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="T27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="U27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="V27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="W27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="X27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Y27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Z27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AA27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AB27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AC27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AD27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AE27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AF27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AG27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AH27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AI27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AJ27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AK27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AL27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AM27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AN27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AO27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AP27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AQ27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AR27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AS27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AT27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AU27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AV27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AW27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AX27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AY27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AZ27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="BA27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="BB27" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="BD27" s="19"/>
     </row>
     <row r="28" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A28" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="B28" s="20" t="s">
-        <v>196</v>
-      </c>
+      <c r="A28" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="B28" s="20"/>
       <c r="C28" s="20" t="s">
-        <v>197</v>
-      </c>
-      <c r="D28" s="20" t="s">
-        <v>198</v>
-      </c>
-      <c r="E28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="F28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="G28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="H28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="I28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="J28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="K28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="L28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="M28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="N28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="O28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="P28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="Q28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="R28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="S28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="T28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="U28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="V28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="W28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="X28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="Y28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="Z28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="AA28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="AB28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="AC28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="AD28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="AE28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="AF28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="AG28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="AH28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="AI28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="AJ28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="AK28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="AL28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="AM28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="AN28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="AO28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="AP28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="AQ28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="AR28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="AS28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="AT28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="AU28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="AV28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="AW28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="AX28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="AY28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="AZ28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="BA28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="BB28" s="14" t="s">
-        <v>199</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="D28" s="20"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="14"/>
+      <c r="N28" s="14"/>
+      <c r="O28" s="14"/>
+      <c r="P28" s="14"/>
+      <c r="Q28" s="14"/>
+      <c r="R28" s="14"/>
+      <c r="S28" s="14"/>
+      <c r="T28" s="14"/>
+      <c r="U28" s="14"/>
+      <c r="V28" s="14"/>
+      <c r="W28" s="14"/>
+      <c r="X28" s="14"/>
+      <c r="Y28" s="14"/>
+      <c r="Z28" s="14"/>
+      <c r="AA28" s="14"/>
+      <c r="AB28" s="14"/>
+      <c r="AC28" s="14"/>
+      <c r="AD28" s="14"/>
+      <c r="AE28" s="14"/>
+      <c r="AF28" s="14"/>
+      <c r="AG28" s="14"/>
+      <c r="AH28" s="14"/>
+      <c r="AI28" s="14"/>
+      <c r="AJ28" s="14"/>
+      <c r="AK28" s="14"/>
+      <c r="AL28" s="14"/>
+      <c r="AM28" s="14"/>
+      <c r="AN28" s="14"/>
+      <c r="AO28" s="14"/>
+      <c r="AP28" s="14"/>
+      <c r="AQ28" s="14"/>
+      <c r="AR28" s="14"/>
+      <c r="AS28" s="14"/>
+      <c r="AT28" s="14"/>
+      <c r="AU28" s="14"/>
+      <c r="AV28" s="14"/>
+      <c r="AW28" s="14"/>
+      <c r="AX28" s="14"/>
+      <c r="AY28" s="14"/>
+      <c r="AZ28" s="14"/>
+      <c r="BA28" s="14"/>
+      <c r="BB28" s="14"/>
       <c r="BD28" s="19"/>
     </row>
     <row r="29" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A29" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="B29" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="B29" s="20"/>
       <c r="C29" s="20" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D29" s="20"/>
       <c r="E29" s="14" t="s">
@@ -5676,9 +5561,11 @@
       <c r="A30" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="B30" s="20"/>
+      <c r="B30" s="20" t="s">
+        <v>203</v>
+      </c>
       <c r="C30" s="20" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D30" s="20"/>
       <c r="E30" s="14"/>
@@ -5735,165 +5622,65 @@
     </row>
     <row r="31" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A31" s="20" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D31" s="20"/>
-      <c r="E31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="F31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="G31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="H31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="I31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="J31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="K31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="L31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="M31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="N31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="O31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="P31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="R31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="S31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="T31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="U31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="V31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="W31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="X31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="Y31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="Z31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="AB31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="AC31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="AD31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="AE31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="AF31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="AG31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="AH31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="AI31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="AJ31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="AK31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="AL31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="AM31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="AN31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="AO31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="AP31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="AQ31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="AR31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="AS31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="AT31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="AU31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="AV31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="AW31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="AX31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="AY31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="AZ31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="BA31" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="BB31" s="14" t="s">
-        <v>205</v>
-      </c>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
+      <c r="N31" s="14"/>
+      <c r="O31" s="14"/>
+      <c r="P31" s="14"/>
+      <c r="Q31" s="14"/>
+      <c r="R31" s="14"/>
+      <c r="S31" s="14"/>
+      <c r="T31" s="14"/>
+      <c r="U31" s="14"/>
+      <c r="V31" s="14"/>
+      <c r="W31" s="14"/>
+      <c r="X31" s="14"/>
+      <c r="Y31" s="14"/>
+      <c r="Z31" s="14"/>
+      <c r="AA31" s="14"/>
+      <c r="AB31" s="14"/>
+      <c r="AC31" s="14"/>
+      <c r="AD31" s="14"/>
+      <c r="AE31" s="14"/>
+      <c r="AF31" s="14"/>
+      <c r="AG31" s="14"/>
+      <c r="AH31" s="14"/>
+      <c r="AI31" s="14"/>
+      <c r="AJ31" s="14"/>
+      <c r="AK31" s="14"/>
+      <c r="AL31" s="14"/>
+      <c r="AM31" s="14"/>
+      <c r="AN31" s="14"/>
+      <c r="AO31" s="14"/>
+      <c r="AP31" s="14"/>
+      <c r="AQ31" s="14"/>
+      <c r="AR31" s="14"/>
+      <c r="AS31" s="14"/>
+      <c r="AT31" s="14"/>
+      <c r="AU31" s="14"/>
+      <c r="AV31" s="14"/>
+      <c r="AW31" s="14"/>
+      <c r="AX31" s="14"/>
+      <c r="AY31" s="14"/>
+      <c r="AZ31" s="14"/>
+      <c r="BA31" s="14"/>
+      <c r="BB31" s="14"/>
       <c r="BD31" s="19"/>
     </row>
     <row r="32" spans="1:56" x14ac:dyDescent="0.25">
@@ -5901,10 +5688,10 @@
         <v>206</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D32" s="20"/>
       <c r="E32" s="14"/>
@@ -5961,13 +5748,13 @@
     </row>
     <row r="33" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A33" s="20" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D33" s="20"/>
       <c r="E33" s="14"/>
@@ -6024,13 +5811,13 @@
     </row>
     <row r="34" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A34" s="20" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D34" s="20"/>
       <c r="E34" s="14"/>
@@ -6087,13 +5874,13 @@
     </row>
     <row r="35" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A35" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D35" s="20"/>
       <c r="E35" s="14"/>
@@ -6150,13 +5937,13 @@
     </row>
     <row r="36" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A36" s="20" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D36" s="20"/>
       <c r="E36" s="14"/>
@@ -6213,13 +6000,13 @@
     </row>
     <row r="37" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A37" s="20" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D37" s="20"/>
       <c r="E37" s="14"/>
@@ -6276,13 +6063,13 @@
     </row>
     <row r="38" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D38" s="20"/>
       <c r="E38" s="14"/>
@@ -6339,13 +6126,13 @@
     </row>
     <row r="39" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A39" s="20" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D39" s="20"/>
       <c r="E39" s="14"/>
@@ -6402,13 +6189,13 @@
     </row>
     <row r="40" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A40" s="20" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D40" s="20"/>
       <c r="E40" s="14"/>
@@ -6464,16 +6251,14 @@
       <c r="BD40" s="19"/>
     </row>
     <row r="41" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A41" s="20" t="s">
-        <v>217</v>
-      </c>
-      <c r="B41" s="20" t="s">
-        <v>209</v>
-      </c>
+      <c r="A41" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="B41" s="14"/>
       <c r="C41" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="D41" s="20"/>
+        <v>155</v>
+      </c>
+      <c r="D41" s="14"/>
       <c r="E41" s="14"/>
       <c r="F41" s="14"/>
       <c r="G41" s="14"/>
@@ -6527,285 +6312,161 @@
       <c r="BD41" s="19"/>
     </row>
     <row r="42" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A42" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="B42" s="20" t="s">
-        <v>209</v>
+      <c r="A42" s="15" t="s">
+        <v>216</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="D42" s="20"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="14"/>
-      <c r="J42" s="14"/>
-      <c r="K42" s="14"/>
-      <c r="L42" s="14"/>
-      <c r="M42" s="14"/>
-      <c r="N42" s="14"/>
-      <c r="O42" s="14"/>
-      <c r="P42" s="14"/>
-      <c r="Q42" s="14"/>
-      <c r="R42" s="14"/>
-      <c r="S42" s="14"/>
-      <c r="T42" s="14"/>
-      <c r="U42" s="14"/>
-      <c r="V42" s="14"/>
-      <c r="W42" s="14"/>
-      <c r="X42" s="14"/>
-      <c r="Y42" s="14"/>
-      <c r="Z42" s="14"/>
-      <c r="AA42" s="14"/>
-      <c r="AB42" s="14"/>
-      <c r="AC42" s="14"/>
-      <c r="AD42" s="14"/>
-      <c r="AE42" s="14"/>
-      <c r="AF42" s="14"/>
-      <c r="AG42" s="14"/>
-      <c r="AH42" s="14"/>
-      <c r="AI42" s="14"/>
-      <c r="AJ42" s="14"/>
-      <c r="AK42" s="14"/>
-      <c r="AL42" s="14"/>
-      <c r="AM42" s="14"/>
-      <c r="AN42" s="14"/>
-      <c r="AO42" s="14"/>
-      <c r="AP42" s="14"/>
-      <c r="AQ42" s="14"/>
-      <c r="AR42" s="14"/>
-      <c r="AS42" s="14"/>
-      <c r="AT42" s="14"/>
-      <c r="AU42" s="14"/>
-      <c r="AV42" s="14"/>
-      <c r="AW42" s="14"/>
-      <c r="AX42" s="14"/>
-      <c r="AY42" s="14"/>
-      <c r="AZ42" s="14"/>
-      <c r="BA42" s="14"/>
-      <c r="BB42" s="14"/>
-      <c r="BD42" s="19"/>
-    </row>
-    <row r="43" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A43" s="14" t="s">
-        <v>219</v>
-      </c>
-      <c r="B43" s="14"/>
-      <c r="C43" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="14"/>
-      <c r="J43" s="14"/>
-      <c r="K43" s="14"/>
-      <c r="L43" s="14"/>
-      <c r="M43" s="14"/>
-      <c r="N43" s="14"/>
-      <c r="O43" s="14"/>
-      <c r="P43" s="14"/>
-      <c r="Q43" s="14"/>
-      <c r="R43" s="14"/>
-      <c r="S43" s="14"/>
-      <c r="T43" s="14"/>
-      <c r="U43" s="14"/>
-      <c r="V43" s="14"/>
-      <c r="W43" s="14"/>
-      <c r="X43" s="14"/>
-      <c r="Y43" s="14"/>
-      <c r="Z43" s="14"/>
-      <c r="AA43" s="14"/>
-      <c r="AB43" s="14"/>
-      <c r="AC43" s="14"/>
-      <c r="AD43" s="14"/>
-      <c r="AE43" s="14"/>
-      <c r="AF43" s="14"/>
-      <c r="AG43" s="14"/>
-      <c r="AH43" s="14"/>
-      <c r="AI43" s="14"/>
-      <c r="AJ43" s="14"/>
-      <c r="AK43" s="14"/>
-      <c r="AL43" s="14"/>
-      <c r="AM43" s="14"/>
-      <c r="AN43" s="14"/>
-      <c r="AO43" s="14"/>
-      <c r="AP43" s="14"/>
-      <c r="AQ43" s="14"/>
-      <c r="AR43" s="14"/>
-      <c r="AS43" s="14"/>
-      <c r="AT43" s="14"/>
-      <c r="AU43" s="14"/>
-      <c r="AV43" s="14"/>
-      <c r="AW43" s="14"/>
-      <c r="AX43" s="14"/>
-      <c r="AY43" s="14"/>
-      <c r="AZ43" s="14"/>
-      <c r="BA43" s="14"/>
-      <c r="BB43" s="14"/>
-      <c r="BD43" s="19"/>
-    </row>
-    <row r="44" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A44" s="15" t="s">
-        <v>220</v>
-      </c>
-      <c r="C44" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="E44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="F44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="G44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="H44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="I44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="J44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="K44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="L44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="M44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="N44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="O44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="P44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="Q44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="R44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="S44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="T44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="U44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="V44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="W44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="X44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="Y44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="Z44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="AA44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="AB44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="AC44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="AD44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="AE44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="AF44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="AG44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="AH44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="AI44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="AJ44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="AK44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="AL44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="AM44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="AN44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="AO44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="AP44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="AQ44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="AR44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="AS44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="AT44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="AU44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="AV44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="AW44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="AX44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="AY44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="AZ44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="BA44" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="BB44" s="15" t="s">
-        <v>221</v>
+        <v>155</v>
+      </c>
+      <c r="E42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="F42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="G42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="H42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="I42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="J42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="K42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="L42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="M42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="N42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="O42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="P42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="R42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="S42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="T42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="U42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="V42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="W42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="X42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="Y42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="Z42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="AA42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="AB42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="AC42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="AD42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="AE42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="AF42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="AG42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="AH42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="AI42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="AJ42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="AK42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="AL42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="AM42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="AN42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="AO42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="AP42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="AQ42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="AR42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="AS42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="AU42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="AW42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="AX42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="AY42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="AZ42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="BA42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="BB42" s="15" t="s">
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -6846,124 +6507,124 @@
   <sheetData>
     <row r="1" spans="1:41" s="24" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="28" t="s">
+        <v>218</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>219</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>263</v>
+      </c>
+      <c r="D1" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="E1" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="F1" s="28" t="s">
+        <v>220</v>
+      </c>
+      <c r="G1" s="32" t="s">
+        <v>235</v>
+      </c>
+      <c r="H1" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="I1" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="J1" s="28" t="s">
         <v>222</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="K1" s="28" t="s">
         <v>223</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="L1" s="28" t="s">
+        <v>237</v>
+      </c>
+      <c r="M1" s="28" t="s">
+        <v>238</v>
+      </c>
+      <c r="N1" s="28" t="s">
+        <v>239</v>
+      </c>
+      <c r="O1" s="28" t="s">
+        <v>266</v>
+      </c>
+      <c r="P1" s="28" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q1" s="28" t="s">
+        <v>240</v>
+      </c>
+      <c r="R1" s="28" t="s">
+        <v>224</v>
+      </c>
+      <c r="S1" s="28" t="s">
+        <v>225</v>
+      </c>
+      <c r="T1" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="U1" s="28" t="s">
+        <v>227</v>
+      </c>
+      <c r="V1" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="W1" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="X1" s="28" t="s">
+        <v>198</v>
+      </c>
+      <c r="Y1" s="28" t="s">
         <v>268</v>
       </c>
-      <c r="D1" s="28" t="s">
-        <v>269</v>
-      </c>
-      <c r="E1" s="28" t="s">
-        <v>270</v>
-      </c>
-      <c r="F1" s="28" t="s">
-        <v>224</v>
-      </c>
-      <c r="G1" s="32" t="s">
-        <v>240</v>
-      </c>
-      <c r="H1" s="28" t="s">
+      <c r="Z1" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="AA1" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="AB1" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="AC1" s="28" t="s">
+        <v>254</v>
+      </c>
+      <c r="AD1" s="28" t="s">
+        <v>243</v>
+      </c>
+      <c r="AE1" s="28" t="s">
+        <v>196</v>
+      </c>
+      <c r="AF1" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="AG1" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="AH1" s="28" t="s">
         <v>241</v>
       </c>
-      <c r="I1" s="28" t="s">
-        <v>225</v>
-      </c>
-      <c r="J1" s="28" t="s">
-        <v>226</v>
-      </c>
-      <c r="K1" s="28" t="s">
-        <v>227</v>
-      </c>
-      <c r="L1" s="28" t="s">
+      <c r="AI1" s="28" t="s">
+        <v>231</v>
+      </c>
+      <c r="AJ1" s="28" t="s">
         <v>242</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>243</v>
-      </c>
-      <c r="N1" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="O1" s="28" t="s">
-        <v>271</v>
-      </c>
-      <c r="P1" s="28" t="s">
-        <v>272</v>
-      </c>
-      <c r="Q1" s="28" t="s">
-        <v>245</v>
-      </c>
-      <c r="R1" s="28" t="s">
-        <v>228</v>
-      </c>
-      <c r="S1" s="28" t="s">
-        <v>229</v>
-      </c>
-      <c r="T1" s="28" t="s">
-        <v>230</v>
-      </c>
-      <c r="U1" s="28" t="s">
-        <v>231</v>
-      </c>
-      <c r="V1" s="28" t="s">
-        <v>186</v>
-      </c>
-      <c r="W1" s="28" t="s">
-        <v>193</v>
-      </c>
-      <c r="X1" s="28" t="s">
-        <v>202</v>
-      </c>
-      <c r="Y1" s="28" t="s">
-        <v>273</v>
-      </c>
-      <c r="Z1" s="28" t="s">
+      <c r="AK1" s="28" t="s">
         <v>232</v>
       </c>
-      <c r="AA1" s="28" t="s">
-        <v>233</v>
-      </c>
-      <c r="AB1" s="28" t="s">
-        <v>234</v>
-      </c>
-      <c r="AC1" s="28" t="s">
-        <v>259</v>
-      </c>
-      <c r="AD1" s="28" t="s">
-        <v>248</v>
-      </c>
-      <c r="AE1" s="28" t="s">
-        <v>200</v>
-      </c>
-      <c r="AF1" s="28" t="s">
-        <v>170</v>
-      </c>
-      <c r="AG1" s="28" t="s">
-        <v>172</v>
-      </c>
-      <c r="AH1" s="28" t="s">
-        <v>246</v>
-      </c>
-      <c r="AI1" s="28" t="s">
-        <v>235</v>
-      </c>
-      <c r="AJ1" s="28" t="s">
-        <v>247</v>
-      </c>
-      <c r="AK1" s="28" t="s">
-        <v>236</v>
-      </c>
       <c r="AL1" s="28" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="AM1" s="28" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="AN1" s="28" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.25">
@@ -7093,19 +6754,19 @@
         <v>Q1</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C5" s="30"/>
       <c r="D5" s="30"/>
       <c r="E5" s="30"/>
       <c r="F5" s="31" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="G5" s="31" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="H5" s="31" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
@@ -7147,19 +6808,19 @@
         <v>Q2</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C6" s="30"/>
       <c r="D6" s="30"/>
       <c r="E6" s="30"/>
       <c r="F6" s="31" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="I6" s="31"/>
       <c r="J6" s="31"/>
@@ -7179,7 +6840,7 @@
       <c r="X6" s="25"/>
       <c r="Y6" s="25"/>
       <c r="Z6" s="25" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="AA6" s="25"/>
       <c r="AB6" s="25"/>
@@ -7203,19 +6864,19 @@
         <v>Q3</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C7" s="30"/>
       <c r="D7" s="30"/>
       <c r="E7" s="30"/>
       <c r="F7" s="31" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="H7" s="31" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="I7" s="31"/>
       <c r="J7" s="31"/>
@@ -7261,19 +6922,19 @@
         <v>Q3</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C8" s="30"/>
       <c r="D8" s="30"/>
       <c r="E8" s="30"/>
       <c r="F8" s="31" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="I8" s="31"/>
       <c r="J8" s="31"/>
@@ -7281,7 +6942,7 @@
       <c r="L8" s="31"/>
       <c r="M8" s="31"/>
       <c r="N8" s="31" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="O8" s="25"/>
       <c r="P8" s="31"/>
@@ -7319,29 +6980,29 @@
         <v>Q3</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C9" s="30"/>
       <c r="D9" s="30"/>
       <c r="E9" s="30"/>
       <c r="F9" s="31" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="H9" s="31" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="I9" s="31"/>
       <c r="J9" s="31"/>
       <c r="K9" s="31"/>
       <c r="L9" s="31" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="M9" s="31"/>
       <c r="N9" s="31" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="O9" s="25"/>
       <c r="P9" s="31"/>
@@ -7379,19 +7040,19 @@
         <v>Q3</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C10" s="30"/>
       <c r="D10" s="30"/>
       <c r="E10" s="30"/>
       <c r="F10" s="31" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="H10" s="31" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="I10" s="31"/>
       <c r="J10" s="31"/>
@@ -7417,13 +7078,13 @@
       <c r="AB10" s="25"/>
       <c r="AC10" s="25"/>
       <c r="AD10" s="14" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="AE10" s="25"/>
       <c r="AF10" s="25"/>
       <c r="AG10" s="25"/>
       <c r="AH10" s="25" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="AI10" s="25"/>
       <c r="AJ10" s="25"/>
@@ -7439,19 +7100,19 @@
         <v>Q3</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C11" s="30"/>
       <c r="D11" s="30"/>
       <c r="E11" s="30"/>
       <c r="F11" s="31" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="H11" s="31" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="I11" s="31"/>
       <c r="J11" s="31"/>
@@ -7459,7 +7120,7 @@
       <c r="L11" s="31"/>
       <c r="M11" s="31"/>
       <c r="N11" s="31" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="O11" s="25"/>
       <c r="P11" s="31"/>
@@ -7483,7 +7144,7 @@
       <c r="AD11" s="14"/>
       <c r="AE11" s="25"/>
       <c r="AF11" s="25" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="AG11" s="25"/>
       <c r="AH11" s="25"/>
@@ -7501,19 +7162,19 @@
         <v>Q3</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C12" s="30"/>
       <c r="D12" s="30"/>
       <c r="E12" s="30"/>
       <c r="F12" s="31" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="H12" s="31" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="I12" s="31"/>
       <c r="J12" s="31"/>
@@ -7521,7 +7182,7 @@
       <c r="L12" s="31"/>
       <c r="M12" s="31"/>
       <c r="N12" s="31" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="O12" s="25"/>
       <c r="P12" s="31"/>
@@ -7543,7 +7204,7 @@
       <c r="AD12" s="14"/>
       <c r="AE12" s="25"/>
       <c r="AF12" s="25" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="AG12" s="25"/>
       <c r="AH12" s="25"/>
@@ -7561,31 +7222,31 @@
         <v>Q4</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="C13" s="30"/>
       <c r="D13" s="30"/>
       <c r="E13" s="30"/>
       <c r="F13" s="31" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="G13" s="31" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="H13" s="31" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="I13" s="31"/>
       <c r="J13" s="31" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="K13" s="31" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="L13" s="31"/>
       <c r="M13" s="31"/>
       <c r="N13" s="31" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="O13" s="25"/>
       <c r="P13" s="31"/>
@@ -7623,19 +7284,19 @@
         <v>Q5</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C14" s="30"/>
       <c r="D14" s="30"/>
       <c r="E14" s="30"/>
       <c r="F14" s="31" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="G14" s="31" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="H14" s="31" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="I14" s="31"/>
       <c r="J14" s="31"/>
@@ -7646,10 +7307,10 @@
       <c r="O14" s="25"/>
       <c r="P14" s="31"/>
       <c r="Q14" s="31" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="R14" s="31" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="S14" s="31"/>
       <c r="T14" s="31"/>
@@ -7681,19 +7342,19 @@
         <v>Q5</v>
       </c>
       <c r="B15" s="30" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C15" s="30"/>
       <c r="D15" s="30"/>
       <c r="E15" s="30"/>
       <c r="F15" s="31" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="G15" s="31" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="H15" s="31" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="I15" s="31"/>
       <c r="J15" s="31"/>
@@ -7704,10 +7365,10 @@
       <c r="O15" s="25"/>
       <c r="P15" s="31"/>
       <c r="Q15" s="31" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="R15" s="31" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="S15" s="25"/>
       <c r="T15" s="25"/>
@@ -7731,7 +7392,7 @@
       <c r="AL15" s="25"/>
       <c r="AM15" s="25"/>
       <c r="AN15" s="25" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="AO15" s="26"/>
     </row>
@@ -7741,19 +7402,19 @@
         <v>Q6</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C16" s="30"/>
       <c r="D16" s="30"/>
       <c r="E16" s="30"/>
       <c r="F16" s="31" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="H16" s="31" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="I16" s="31"/>
       <c r="J16" s="31"/>
@@ -7789,7 +7450,7 @@
       <c r="AJ16" s="25"/>
       <c r="AK16" s="25"/>
       <c r="AL16" s="31" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="AM16" s="25"/>
       <c r="AN16" s="25"/>
@@ -7801,26 +7462,26 @@
         <v>Q6</v>
       </c>
       <c r="B17" s="30" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C17" s="30"/>
       <c r="D17" s="30"/>
       <c r="E17" s="30"/>
       <c r="F17" s="31" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="G17" s="31" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="H17" s="31" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="I17" s="31"/>
       <c r="J17" s="31" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="K17" s="31" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="L17" s="31"/>
       <c r="M17" s="31"/>
@@ -7859,24 +7520,24 @@
         <v>Q9</v>
       </c>
       <c r="B18" s="30" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C18" s="30"/>
       <c r="D18" s="30"/>
       <c r="E18" s="30"/>
       <c r="F18" s="31"/>
       <c r="G18" s="31" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="H18" s="31" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="I18" s="31"/>
       <c r="J18" s="31" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="K18" s="31" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="L18" s="31"/>
       <c r="M18" s="31"/>
@@ -7886,10 +7547,10 @@
       <c r="Q18" s="31"/>
       <c r="R18" s="31"/>
       <c r="S18" s="31" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="T18" s="31" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="U18" s="25"/>
       <c r="V18" s="25"/>
@@ -7919,24 +7580,24 @@
         <v>Q9</v>
       </c>
       <c r="B19" s="30" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C19" s="30"/>
       <c r="D19" s="30"/>
       <c r="E19" s="30"/>
       <c r="F19" s="31"/>
       <c r="G19" s="31" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="H19" s="31" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="I19" s="31"/>
       <c r="J19" s="31" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="K19" s="31" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="L19" s="31"/>
       <c r="M19" s="31"/>
@@ -7946,10 +7607,10 @@
       <c r="Q19" s="31"/>
       <c r="R19" s="31"/>
       <c r="S19" s="31" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="T19" s="31" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="U19" s="25"/>
       <c r="V19" s="25"/>
@@ -7979,26 +7640,26 @@
         <v>Q9</v>
       </c>
       <c r="B20" s="30" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C20" s="30"/>
       <c r="D20" s="30"/>
       <c r="E20" s="30"/>
       <c r="F20" s="31" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="G20" s="31" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="H20" s="31" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="I20" s="31"/>
       <c r="J20" s="31" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="K20" s="31" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="L20" s="31"/>
       <c r="M20" s="31"/>
@@ -8008,10 +7669,10 @@
       <c r="Q20" s="31"/>
       <c r="R20" s="31"/>
       <c r="S20" s="31" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="T20" s="31" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="U20" s="25"/>
       <c r="V20" s="25"/>
@@ -8041,16 +7702,16 @@
         <v>QNOT CHECKED: 2</v>
       </c>
       <c r="B21" s="30" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C21" s="30"/>
       <c r="D21" s="30"/>
       <c r="E21" s="30"/>
       <c r="F21" s="31" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="G21" s="31" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="H21" s="31"/>
       <c r="I21" s="31"/>
@@ -8064,10 +7725,10 @@
       <c r="Q21" s="31"/>
       <c r="R21" s="31"/>
       <c r="S21" s="31" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="T21" s="31" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="U21" s="25"/>
       <c r="V21" s="25"/>
@@ -8075,7 +7736,7 @@
       <c r="X21" s="25"/>
       <c r="Y21" s="25"/>
       <c r="Z21" s="25" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="AA21" s="25"/>
       <c r="AB21" s="25"/>
@@ -8099,19 +7760,19 @@
         <v>Qmulti selvar with unguelt: 2</v>
       </c>
       <c r="B22" s="30" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="C22" s="30"/>
       <c r="D22" s="30"/>
       <c r="E22" s="30"/>
       <c r="F22" s="31" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="G22" s="31" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="H22" s="31" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="I22" s="31"/>
       <c r="J22" s="31"/>
@@ -8124,10 +7785,10 @@
       <c r="Q22" s="31"/>
       <c r="R22" s="31"/>
       <c r="S22" s="31" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="T22" s="31" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="U22" s="25"/>
       <c r="V22" s="25"/>
@@ -8157,19 +7818,19 @@
         <v>Qtrigger invalid values: 2</v>
       </c>
       <c r="B23" s="30" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="C23" s="30"/>
       <c r="D23" s="30"/>
       <c r="E23" s="30"/>
       <c r="F23" s="31" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="G23" s="31" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="H23" s="31" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="I23" s="31"/>
       <c r="J23" s="31"/>
@@ -8211,19 +7872,19 @@
         <v>QNOT CHECKED: 5</v>
       </c>
       <c r="B24" s="30" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="C24" s="30"/>
       <c r="D24" s="30"/>
       <c r="E24" s="30"/>
       <c r="F24" s="31" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="G24" s="31" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="H24" s="31" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="I24" s="31"/>
       <c r="J24" s="31"/>
@@ -8234,16 +7895,16 @@
       <c r="O24" s="25"/>
       <c r="P24" s="31"/>
       <c r="Q24" s="31" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="R24" s="31" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="S24" s="31" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="T24" s="31" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="U24" s="25"/>
       <c r="V24" s="25"/>
@@ -8273,41 +7934,41 @@
         <v>Q7</v>
       </c>
       <c r="B25" s="30" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C25" s="30"/>
       <c r="D25" s="30"/>
       <c r="E25" s="30"/>
       <c r="F25" s="31" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G25" s="31" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="H25" s="31" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="I25" s="31"/>
       <c r="J25" s="31" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K25" s="31" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="L25" s="31"/>
       <c r="M25" s="31"/>
       <c r="N25" s="31" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="O25" s="25"/>
       <c r="P25" s="31"/>
       <c r="Q25" s="31"/>
       <c r="R25" s="31"/>
       <c r="S25" s="31" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="T25" s="31" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="U25" s="25"/>
       <c r="V25" s="25"/>
@@ -8327,7 +7988,7 @@
       <c r="AJ25" s="25"/>
       <c r="AK25" s="25"/>
       <c r="AL25" s="31" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="AM25" s="25"/>
       <c r="AN25" s="25"/>

--- a/tests/testthat/excel/mapping_neu_weighted.xlsx
+++ b/tests/testthat/excel/mapping_neu_weighted.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\Projects\UW git\crosstabser\tests\testthat\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F9B2EF-4064-4F05-830F-E4DC2DECE23E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3062D0D8-FD6C-4509-B454-1E33A2E4FC75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15045" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15045" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -1050,9 +1050,6 @@
     <t xml:space="preserve">(1 THRU 2 = 1) (3 THRU 5 = 2) (6 THRU HI = 3) </t>
   </si>
   <si>
-    <t xml:space="preserve">1 '1-2mal' 2 '3-5mal' 3 '&gt;5mal' </t>
-  </si>
-  <si>
     <t>S1E2M0</t>
   </si>
   <si>
@@ -1192,6 +1189,9 @@
   </si>
   <si>
     <t>Invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 "1-2mal" 2 '3-5mal' 3 '&gt;5mal' </t>
   </si>
 </sst>
 </file>
@@ -2628,7 +2628,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="33" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B35" s="34">
         <v>-2</v>
@@ -3273,7 +3273,7 @@
     </row>
     <row r="6" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A6" s="27" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B6" s="20" t="s">
         <v>152</v>
@@ -3285,154 +3285,154 @@
         <v>154</v>
       </c>
       <c r="E6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="O6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="P6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Q6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="R6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="S6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="T6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="U6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="V6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="W6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="X6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Y6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Z6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AA6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AB6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AC6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AD6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AE6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AF6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AH6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AI6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AJ6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AK6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AL6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AM6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AN6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AO6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AP6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AQ6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AR6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AS6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AT6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AU6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AV6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AW6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AX6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AY6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AZ6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="BA6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="BB6" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="BD6" s="19"/>
     </row>
@@ -6817,7 +6817,7 @@
         <v>248</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H6" s="31" t="s">
         <v>260</v>
@@ -6840,7 +6840,7 @@
       <c r="X6" s="25"/>
       <c r="Y6" s="25"/>
       <c r="Z6" s="25" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AA6" s="25"/>
       <c r="AB6" s="25"/>
@@ -6931,7 +6931,7 @@
         <v>233</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H8" s="31" t="s">
         <v>262</v>
@@ -6998,11 +6998,11 @@
       <c r="J9" s="31"/>
       <c r="K9" s="31"/>
       <c r="L9" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="M9" s="31"/>
       <c r="N9" s="31" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O9" s="25"/>
       <c r="P9" s="31"/>
@@ -7171,7 +7171,7 @@
         <v>233</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H12" s="31" t="s">
         <v>262</v>
@@ -7241,12 +7241,12 @@
         <v>279</v>
       </c>
       <c r="K13" s="31" t="s">
-        <v>280</v>
+        <v>327</v>
       </c>
       <c r="L13" s="31"/>
       <c r="M13" s="31"/>
       <c r="N13" s="31" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O13" s="25"/>
       <c r="P13" s="31"/>
@@ -7296,7 +7296,7 @@
         <v>252</v>
       </c>
       <c r="H14" s="31" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I14" s="31"/>
       <c r="J14" s="31"/>
@@ -7310,7 +7310,7 @@
         <v>253</v>
       </c>
       <c r="R14" s="31" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="S14" s="31"/>
       <c r="T14" s="31"/>
@@ -7368,7 +7368,7 @@
         <v>253</v>
       </c>
       <c r="R15" s="31" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="S15" s="25"/>
       <c r="T15" s="25"/>
@@ -7392,7 +7392,7 @@
       <c r="AL15" s="25"/>
       <c r="AM15" s="25"/>
       <c r="AN15" s="25" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AO15" s="26"/>
     </row>
@@ -7402,7 +7402,7 @@
         <v>Q6</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C16" s="30"/>
       <c r="D16" s="30"/>
@@ -7411,10 +7411,10 @@
         <v>234</v>
       </c>
       <c r="G16" s="31" t="s">
+        <v>288</v>
+      </c>
+      <c r="H16" s="31" t="s">
         <v>289</v>
-      </c>
-      <c r="H16" s="31" t="s">
-        <v>290</v>
       </c>
       <c r="I16" s="31"/>
       <c r="J16" s="31"/>
@@ -7450,7 +7450,7 @@
       <c r="AJ16" s="25"/>
       <c r="AK16" s="25"/>
       <c r="AL16" s="31" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AM16" s="25"/>
       <c r="AN16" s="25"/>
@@ -7462,7 +7462,7 @@
         <v>Q6</v>
       </c>
       <c r="B17" s="30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C17" s="30"/>
       <c r="D17" s="30"/>
@@ -7471,17 +7471,17 @@
         <v>233</v>
       </c>
       <c r="G17" s="31" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H17" s="31" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I17" s="31"/>
       <c r="J17" s="31" t="s">
+        <v>295</v>
+      </c>
+      <c r="K17" s="31" t="s">
         <v>296</v>
-      </c>
-      <c r="K17" s="31" t="s">
-        <v>297</v>
       </c>
       <c r="L17" s="31"/>
       <c r="M17" s="31"/>
@@ -7520,24 +7520,24 @@
         <v>Q9</v>
       </c>
       <c r="B18" s="30" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C18" s="30"/>
       <c r="D18" s="30"/>
       <c r="E18" s="30"/>
       <c r="F18" s="31"/>
       <c r="G18" s="31" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H18" s="31" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I18" s="31"/>
       <c r="J18" s="31" t="s">
+        <v>298</v>
+      </c>
+      <c r="K18" s="31" t="s">
         <v>299</v>
-      </c>
-      <c r="K18" s="31" t="s">
-        <v>300</v>
       </c>
       <c r="L18" s="31"/>
       <c r="M18" s="31"/>
@@ -7547,10 +7547,10 @@
       <c r="Q18" s="31"/>
       <c r="R18" s="31"/>
       <c r="S18" s="31" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="T18" s="31" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="U18" s="25"/>
       <c r="V18" s="25"/>
@@ -7580,24 +7580,24 @@
         <v>Q9</v>
       </c>
       <c r="B19" s="30" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C19" s="30"/>
       <c r="D19" s="30"/>
       <c r="E19" s="30"/>
       <c r="F19" s="31"/>
       <c r="G19" s="31" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H19" s="31" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I19" s="31"/>
       <c r="J19" s="31" t="s">
+        <v>298</v>
+      </c>
+      <c r="K19" s="31" t="s">
         <v>299</v>
-      </c>
-      <c r="K19" s="31" t="s">
-        <v>300</v>
       </c>
       <c r="L19" s="31"/>
       <c r="M19" s="31"/>
@@ -7607,10 +7607,10 @@
       <c r="Q19" s="31"/>
       <c r="R19" s="31"/>
       <c r="S19" s="31" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="T19" s="31" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="U19" s="25"/>
       <c r="V19" s="25"/>
@@ -7640,7 +7640,7 @@
         <v>Q9</v>
       </c>
       <c r="B20" s="30" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C20" s="30"/>
       <c r="D20" s="30"/>
@@ -7649,17 +7649,17 @@
         <v>233</v>
       </c>
       <c r="G20" s="31" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H20" s="31" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I20" s="31"/>
       <c r="J20" s="31" t="s">
+        <v>298</v>
+      </c>
+      <c r="K20" s="31" t="s">
         <v>299</v>
-      </c>
-      <c r="K20" s="31" t="s">
-        <v>300</v>
       </c>
       <c r="L20" s="31"/>
       <c r="M20" s="31"/>
@@ -7669,10 +7669,10 @@
       <c r="Q20" s="31"/>
       <c r="R20" s="31"/>
       <c r="S20" s="31" t="s">
+        <v>302</v>
+      </c>
+      <c r="T20" s="31" t="s">
         <v>303</v>
-      </c>
-      <c r="T20" s="31" t="s">
-        <v>304</v>
       </c>
       <c r="U20" s="25"/>
       <c r="V20" s="25"/>
@@ -7702,7 +7702,7 @@
         <v>QNOT CHECKED: 2</v>
       </c>
       <c r="B21" s="30" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C21" s="30"/>
       <c r="D21" s="30"/>
@@ -7711,7 +7711,7 @@
         <v>248</v>
       </c>
       <c r="G21" s="31" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H21" s="31"/>
       <c r="I21" s="31"/>
@@ -7725,10 +7725,10 @@
       <c r="Q21" s="31"/>
       <c r="R21" s="31"/>
       <c r="S21" s="31" t="s">
+        <v>302</v>
+      </c>
+      <c r="T21" s="31" t="s">
         <v>303</v>
-      </c>
-      <c r="T21" s="31" t="s">
-        <v>304</v>
       </c>
       <c r="U21" s="25"/>
       <c r="V21" s="25"/>
@@ -7736,7 +7736,7 @@
       <c r="X21" s="25"/>
       <c r="Y21" s="25"/>
       <c r="Z21" s="25" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AA21" s="25"/>
       <c r="AB21" s="25"/>
@@ -7760,7 +7760,7 @@
         <v>Qmulti selvar with unguelt: 2</v>
       </c>
       <c r="B22" s="30" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C22" s="30"/>
       <c r="D22" s="30"/>
@@ -7769,10 +7769,10 @@
         <v>248</v>
       </c>
       <c r="G22" s="31" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H22" s="31" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I22" s="31"/>
       <c r="J22" s="31"/>
@@ -7785,10 +7785,10 @@
       <c r="Q22" s="31"/>
       <c r="R22" s="31"/>
       <c r="S22" s="31" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="T22" s="31" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="U22" s="25"/>
       <c r="V22" s="25"/>
@@ -7818,7 +7818,7 @@
         <v>Qtrigger invalid values: 2</v>
       </c>
       <c r="B23" s="30" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C23" s="30"/>
       <c r="D23" s="30"/>
@@ -7827,10 +7827,10 @@
         <v>248</v>
       </c>
       <c r="G23" s="31" t="s">
+        <v>322</v>
+      </c>
+      <c r="H23" s="31" t="s">
         <v>323</v>
-      </c>
-      <c r="H23" s="31" t="s">
-        <v>324</v>
       </c>
       <c r="I23" s="31"/>
       <c r="J23" s="31"/>
@@ -7872,7 +7872,7 @@
         <v>QNOT CHECKED: 5</v>
       </c>
       <c r="B24" s="30" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C24" s="30"/>
       <c r="D24" s="30"/>
@@ -7881,10 +7881,10 @@
         <v>251</v>
       </c>
       <c r="G24" s="31" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H24" s="31" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I24" s="31"/>
       <c r="J24" s="31"/>
@@ -7898,13 +7898,13 @@
         <v>253</v>
       </c>
       <c r="R24" s="31" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="S24" s="31" t="s">
+        <v>302</v>
+      </c>
+      <c r="T24" s="31" t="s">
         <v>303</v>
-      </c>
-      <c r="T24" s="31" t="s">
-        <v>304</v>
       </c>
       <c r="U24" s="25"/>
       <c r="V24" s="25"/>
@@ -7934,7 +7934,7 @@
         <v>Q7</v>
       </c>
       <c r="B25" s="30" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C25" s="30"/>
       <c r="D25" s="30"/>
@@ -7943,32 +7943,32 @@
         <v>234</v>
       </c>
       <c r="G25" s="31" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H25" s="31" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I25" s="31"/>
       <c r="J25" s="31" t="s">
+        <v>312</v>
+      </c>
+      <c r="K25" s="31" t="s">
         <v>313</v>
-      </c>
-      <c r="K25" s="31" t="s">
-        <v>314</v>
       </c>
       <c r="L25" s="31"/>
       <c r="M25" s="31"/>
       <c r="N25" s="31" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O25" s="25"/>
       <c r="P25" s="31"/>
       <c r="Q25" s="31"/>
       <c r="R25" s="31"/>
       <c r="S25" s="31" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="T25" s="31" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="U25" s="25"/>
       <c r="V25" s="25"/>
@@ -7988,7 +7988,7 @@
       <c r="AJ25" s="25"/>
       <c r="AK25" s="25"/>
       <c r="AL25" s="31" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AM25" s="25"/>
       <c r="AN25" s="25"/>

--- a/tests/testthat/excel/mapping_neu_weighted.xlsx
+++ b/tests/testthat/excel/mapping_neu_weighted.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\Projects\UW git\crosstabser\tests\testthat\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3062D0D8-FD6C-4509-B454-1E33A2E4FC75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D40E735F-EA85-4A3E-BB81-8AFE2694DA66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15045" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15045" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
   </externalReferences>
   <definedNames>
     <definedName name="R_miss_rec_val">Config!$B$35</definedName>
+    <definedName name="V_BookNo">Config!$B$11</definedName>
     <definedName name="V_Datum">Config!$B$18</definedName>
     <definedName name="V_ErrCountLog10">#REF!</definedName>
     <definedName name="V_ErrCountLog20">#REF!</definedName>
@@ -208,7 +209,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="329">
   <si>
     <t>Make script</t>
   </si>
@@ -1193,6 +1194,9 @@
   <si>
     <t xml:space="preserve">1 "1-2mal" 2 '3-5mal' 3 '&gt;5mal' </t>
   </si>
+  <si>
+    <t>V_BookNo</t>
+  </si>
 </sst>
 </file>
 
@@ -1438,13 +1442,13 @@
     <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="1" quotePrefix="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="1" quotePrefix="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -2460,7 +2464,12 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B11" s="10"/>
+      <c r="A11" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B11" s="10">
+        <v>999999999</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
@@ -2892,8 +2901,8 @@
     </row>
     <row r="2" spans="1:56" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:56" s="18" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="35"/>
-      <c r="B3" s="36"/>
+      <c r="A3" s="36"/>
+      <c r="B3" s="37"/>
       <c r="E3" s="18">
         <v>1</v>
       </c>
@@ -3047,8 +3056,8 @@
       <c r="BD3" s="19"/>
     </row>
     <row r="4" spans="1:56" s="18" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="35"/>
-      <c r="B4" s="36"/>
+      <c r="A4" s="36"/>
+      <c r="B4" s="37"/>
       <c r="E4" s="18" t="s">
         <v>15</v>
       </c>
@@ -3284,154 +3293,154 @@
       <c r="D6" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="E6" s="37" t="s">
+      <c r="E6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="F6" s="37" t="s">
+      <c r="F6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="G6" s="37" t="s">
+      <c r="G6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="H6" s="37" t="s">
+      <c r="H6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="I6" s="37" t="s">
+      <c r="I6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="J6" s="37" t="s">
+      <c r="J6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="K6" s="37" t="s">
+      <c r="K6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="L6" s="37" t="s">
+      <c r="L6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="M6" s="37" t="s">
+      <c r="M6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="N6" s="37" t="s">
+      <c r="N6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="O6" s="37" t="s">
+      <c r="O6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="P6" s="37" t="s">
+      <c r="P6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="Q6" s="37" t="s">
+      <c r="Q6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="R6" s="37" t="s">
+      <c r="R6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="S6" s="37" t="s">
+      <c r="S6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="T6" s="37" t="s">
+      <c r="T6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="U6" s="37" t="s">
+      <c r="U6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="V6" s="37" t="s">
+      <c r="V6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="W6" s="37" t="s">
+      <c r="W6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="X6" s="37" t="s">
+      <c r="X6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="Y6" s="37" t="s">
+      <c r="Y6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="Z6" s="37" t="s">
+      <c r="Z6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="AA6" s="37" t="s">
+      <c r="AA6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="AB6" s="37" t="s">
+      <c r="AB6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="AC6" s="37" t="s">
+      <c r="AC6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="AD6" s="37" t="s">
+      <c r="AD6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="AE6" s="37" t="s">
+      <c r="AE6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="AF6" s="37" t="s">
+      <c r="AF6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="AG6" s="37" t="s">
+      <c r="AG6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="AH6" s="37" t="s">
+      <c r="AH6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="AI6" s="37" t="s">
+      <c r="AI6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="AJ6" s="37" t="s">
+      <c r="AJ6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="AK6" s="37" t="s">
+      <c r="AK6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="AL6" s="37" t="s">
+      <c r="AL6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="AM6" s="37" t="s">
+      <c r="AM6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="AN6" s="37" t="s">
+      <c r="AN6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="AO6" s="37" t="s">
+      <c r="AO6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="AP6" s="37" t="s">
+      <c r="AP6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="AQ6" s="37" t="s">
+      <c r="AQ6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="AR6" s="37" t="s">
+      <c r="AR6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="AS6" s="37" t="s">
+      <c r="AS6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="AT6" s="37" t="s">
+      <c r="AT6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="AU6" s="37" t="s">
+      <c r="AU6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="AV6" s="37" t="s">
+      <c r="AV6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="AW6" s="37" t="s">
+      <c r="AW6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="AX6" s="37" t="s">
+      <c r="AX6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="AY6" s="37" t="s">
+      <c r="AY6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="AZ6" s="37" t="s">
+      <c r="AZ6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="BA6" s="37" t="s">
+      <c r="BA6" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="BB6" s="37" t="s">
+      <c r="BB6" s="35" t="s">
         <v>325</v>
       </c>
       <c r="BD6" s="19"/>

--- a/tests/testthat/excel/mapping_neu_weighted.xlsx
+++ b/tests/testthat/excel/mapping_neu_weighted.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\Projects\UW git\crosstabser\tests\testthat\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D40E735F-EA85-4A3E-BB81-8AFE2694DA66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B06889-7736-4C0F-AE6D-6F8E7A2C8510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15045" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15045" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -209,7 +209,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="350">
   <si>
     <t>Make script</t>
   </si>
@@ -1196,6 +1196,69 @@
   </si>
   <si>
     <t>V_BookNo</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>Q2</t>
+  </si>
+  <si>
+    <t>Q3_1</t>
+  </si>
+  <si>
+    <t>Q3_2</t>
+  </si>
+  <si>
+    <t>Q3_3</t>
+  </si>
+  <si>
+    <t>Q3_4</t>
+  </si>
+  <si>
+    <t>Q3_5</t>
+  </si>
+  <si>
+    <t>Q3_6</t>
+  </si>
+  <si>
+    <t>Q4</t>
+  </si>
+  <si>
+    <t>Q5_1</t>
+  </si>
+  <si>
+    <t>Q5_2</t>
+  </si>
+  <si>
+    <t>Q6_1</t>
+  </si>
+  <si>
+    <t>Q6_2</t>
+  </si>
+  <si>
+    <t>Q9_1</t>
+  </si>
+  <si>
+    <t>Q9_2</t>
+  </si>
+  <si>
+    <t>Q9_3</t>
+  </si>
+  <si>
+    <t>QNOT CHECKED: 2</t>
+  </si>
+  <si>
+    <t>Qmulti selvar with unguelt: 2</t>
+  </si>
+  <si>
+    <t>Qtrigger invalid values: 2</t>
+  </si>
+  <si>
+    <t>QNOT CHECKED: 5</t>
+  </si>
+  <si>
+    <t>Q7</t>
   </si>
 </sst>
 </file>
@@ -6758,9 +6821,8 @@
       <c r="AO4" s="26"/>
     </row>
     <row r="5" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A5" s="30" t="str">
-        <f>"Q"&amp;LEFT(B5,FIND(".",B5)-1)</f>
-        <v>Q1</v>
+      <c r="A5" s="30" t="s">
+        <v>329</v>
       </c>
       <c r="B5" s="30" t="s">
         <v>245</v>
@@ -6812,9 +6874,8 @@
       <c r="AO5" s="26"/>
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A6" s="30" t="str">
-        <f t="shared" ref="A6:A14" si="0">"Q"&amp;LEFT(B6,FIND(".",B6)-1)</f>
-        <v>Q2</v>
+      <c r="A6" s="30" t="s">
+        <v>330</v>
       </c>
       <c r="B6" s="30" t="s">
         <v>247</v>
@@ -6868,9 +6929,8 @@
       <c r="AO6" s="26"/>
     </row>
     <row r="7" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A7" s="30" t="str">
-        <f t="shared" si="0"/>
-        <v>Q3</v>
+      <c r="A7" s="30" t="s">
+        <v>331</v>
       </c>
       <c r="B7" s="30" t="s">
         <v>249</v>
@@ -6926,9 +6986,8 @@
       <c r="AO7" s="26"/>
     </row>
     <row r="8" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A8" s="30" t="str">
-        <f t="shared" ref="A8" si="1">"Q"&amp;LEFT(B8,FIND(".",B8)-1)</f>
-        <v>Q3</v>
+      <c r="A8" s="30" t="s">
+        <v>332</v>
       </c>
       <c r="B8" s="30" t="s">
         <v>249</v>
@@ -6984,9 +7043,8 @@
       <c r="AO8" s="26"/>
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A9" s="30" t="str">
-        <f t="shared" ref="A9" si="2">"Q"&amp;LEFT(B9,FIND(".",B9)-1)</f>
-        <v>Q3</v>
+      <c r="A9" s="30" t="s">
+        <v>333</v>
       </c>
       <c r="B9" s="30" t="s">
         <v>249</v>
@@ -7044,9 +7102,8 @@
       <c r="AO9" s="26"/>
     </row>
     <row r="10" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A10" s="30" t="str">
-        <f t="shared" ref="A10" si="3">"Q"&amp;LEFT(B10,FIND(".",B10)-1)</f>
-        <v>Q3</v>
+      <c r="A10" s="30" t="s">
+        <v>334</v>
       </c>
       <c r="B10" s="30" t="s">
         <v>249</v>
@@ -7104,9 +7161,8 @@
       <c r="AO10" s="26"/>
     </row>
     <row r="11" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A11" s="30" t="str">
-        <f t="shared" ref="A11:A13" si="4">"Q"&amp;LEFT(B11,FIND(".",B11)-1)</f>
-        <v>Q3</v>
+      <c r="A11" s="30" t="s">
+        <v>335</v>
       </c>
       <c r="B11" s="30" t="s">
         <v>249</v>
@@ -7166,9 +7222,8 @@
       <c r="AO11" s="26"/>
     </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A12" s="30" t="str">
-        <f t="shared" ref="A12" si="5">"Q"&amp;LEFT(B12,FIND(".",B12)-1)</f>
-        <v>Q3</v>
+      <c r="A12" s="30" t="s">
+        <v>336</v>
       </c>
       <c r="B12" s="30" t="s">
         <v>249</v>
@@ -7226,9 +7281,8 @@
       <c r="AO12" s="26"/>
     </row>
     <row r="13" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A13" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Q4</v>
+      <c r="A13" s="30" t="s">
+        <v>337</v>
       </c>
       <c r="B13" s="30" t="s">
         <v>277</v>
@@ -7288,9 +7342,8 @@
       <c r="AO13" s="26"/>
     </row>
     <row r="14" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A14" s="30" t="str">
-        <f t="shared" si="0"/>
-        <v>Q5</v>
+      <c r="A14" s="30" t="s">
+        <v>338</v>
       </c>
       <c r="B14" s="30" t="s">
         <v>250</v>
@@ -7346,9 +7399,8 @@
       <c r="AO14" s="26"/>
     </row>
     <row r="15" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A15" s="30" t="str">
-        <f t="shared" ref="A15:A16" si="6">"Q"&amp;LEFT(B15,FIND(".",B15)-1)</f>
-        <v>Q5</v>
+      <c r="A15" s="30" t="s">
+        <v>339</v>
       </c>
       <c r="B15" s="30" t="s">
         <v>250</v>
@@ -7406,9 +7458,8 @@
       <c r="AO15" s="26"/>
     </row>
     <row r="16" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A16" s="30" t="str">
-        <f t="shared" si="6"/>
-        <v>Q6</v>
+      <c r="A16" s="30" t="s">
+        <v>340</v>
       </c>
       <c r="B16" s="30" t="s">
         <v>287</v>
@@ -7466,9 +7517,8 @@
       <c r="AO16" s="26"/>
     </row>
     <row r="17" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A17" s="30" t="str">
-        <f t="shared" ref="A17:A18" si="7">"Q"&amp;LEFT(B17,FIND(".",B17)-1)</f>
-        <v>Q6</v>
+      <c r="A17" s="30" t="s">
+        <v>341</v>
       </c>
       <c r="B17" s="30" t="s">
         <v>287</v>
@@ -7524,9 +7574,8 @@
       <c r="AO17" s="26"/>
     </row>
     <row r="18" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A18" s="30" t="str">
-        <f t="shared" si="7"/>
-        <v>Q9</v>
+      <c r="A18" s="30" t="s">
+        <v>342</v>
       </c>
       <c r="B18" s="30" t="s">
         <v>297</v>
@@ -7584,9 +7633,8 @@
       <c r="AO18" s="26"/>
     </row>
     <row r="19" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A19" s="30" t="str">
-        <f t="shared" ref="A19:A25" si="8">"Q"&amp;LEFT(B19,FIND(".",B19)-1)</f>
-        <v>Q9</v>
+      <c r="A19" s="30" t="s">
+        <v>343</v>
       </c>
       <c r="B19" s="30" t="s">
         <v>297</v>
@@ -7644,9 +7692,8 @@
       <c r="AO19" s="26"/>
     </row>
     <row r="20" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A20" s="30" t="str">
-        <f t="shared" si="8"/>
-        <v>Q9</v>
+      <c r="A20" s="30" t="s">
+        <v>344</v>
       </c>
       <c r="B20" s="30" t="s">
         <v>297</v>
@@ -7706,9 +7753,8 @@
       <c r="AO20" s="26"/>
     </row>
     <row r="21" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A21" s="30" t="str">
-        <f t="shared" si="8"/>
-        <v>QNOT CHECKED: 2</v>
+      <c r="A21" s="30" t="s">
+        <v>345</v>
       </c>
       <c r="B21" s="30" t="s">
         <v>309</v>
@@ -7764,9 +7810,8 @@
       <c r="AO21" s="26"/>
     </row>
     <row r="22" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A22" s="30" t="str">
-        <f t="shared" ref="A22" si="9">"Q"&amp;LEFT(B22,FIND(".",B22)-1)</f>
-        <v>Qmulti selvar with unguelt: 2</v>
+      <c r="A22" s="30" t="s">
+        <v>346</v>
       </c>
       <c r="B22" s="30" t="s">
         <v>319</v>
@@ -7822,9 +7867,8 @@
       <c r="AO22" s="26"/>
     </row>
     <row r="23" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A23" s="30" t="str">
-        <f t="shared" ref="A23" si="10">"Q"&amp;LEFT(B23,FIND(".",B23)-1)</f>
-        <v>Qtrigger invalid values: 2</v>
+      <c r="A23" s="30" t="s">
+        <v>347</v>
       </c>
       <c r="B23" s="30" t="s">
         <v>321</v>
@@ -7876,9 +7920,8 @@
       <c r="AO23" s="26"/>
     </row>
     <row r="24" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A24" s="30" t="str">
-        <f t="shared" si="8"/>
-        <v>QNOT CHECKED: 5</v>
+      <c r="A24" s="30" t="s">
+        <v>348</v>
       </c>
       <c r="B24" s="30" t="s">
         <v>310</v>
@@ -7938,9 +7981,8 @@
       <c r="AO24" s="26"/>
     </row>
     <row r="25" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A25" s="30" t="str">
-        <f t="shared" si="8"/>
-        <v>Q7</v>
+      <c r="A25" s="30" t="s">
+        <v>349</v>
       </c>
       <c r="B25" s="30" t="s">
         <v>311</v>

--- a/tests/testthat/excel/mapping_neu_weighted.xlsx
+++ b/tests/testthat/excel/mapping_neu_weighted.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\Projects\UW git\crosstabser\tests\testthat\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B06889-7736-4C0F-AE6D-6F8E7A2C8510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{526D824F-5BD9-417C-93ED-4329C733A5BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15045" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -209,7 +209,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="351">
   <si>
     <t>Make script</t>
   </si>
@@ -1259,6 +1259,9 @@
   </si>
   <si>
     <t>Q7</t>
+  </si>
+  <si>
+    <t>Checks</t>
   </si>
 </sst>
 </file>
@@ -6698,6 +6701,9 @@
       <c r="AN1" s="28" t="s">
         <v>257</v>
       </c>
+      <c r="AO1" s="24" t="s">
+        <v>350</v>
+      </c>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A2" s="19"/>
